--- a/billOfMaterials.xlsx
+++ b/billOfMaterials.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OnionSAT\Desktop\sc26-camera-modul-pcb\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OnionSAT\Desktop\camera-modul\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1098C83E-F008-4B52-9DD1-F83280B3AB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260C4BF7-593A-4115-8186-5D4996097043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{50AE749F-2407-4433-B18E-5C6A4D35D76C}"/>
   </bookViews>
@@ -36,19 +36,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Component</t>
+  </si>
+  <si>
+    <t>Beszerzési hely</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C114408.html?s_z=n_stm32h743zit6</t>
+  </si>
+  <si>
+    <t>Stm32h743zit6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="238"/>
@@ -72,13 +90,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hivatkozás" xfId="1" builtinId="8"/>
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -411,15 +432,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3876E43-79AD-4CB7-B6DE-977DB3E58EB9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{3B843B76-4971-46CD-B8F3-C12257D6B3FA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/billOfMaterials.xlsx
+++ b/billOfMaterials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OnionSAT\Desktop\camera-modul\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260C4BF7-593A-4115-8186-5D4996097043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9D104E-5CDE-4FFF-B83B-44E579FF80B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{50AE749F-2407-4433-B18E-5C6A4D35D76C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Component</t>
   </si>
@@ -48,13 +48,31 @@
   </si>
   <si>
     <t>Stm32h743zit6</t>
+  </si>
+  <si>
+    <t>https://www.hestore.hu/prod_10046018.html</t>
+  </si>
+  <si>
+    <t>IS42S16800F-5TLI</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C2995536.html?s_z=h_sim7600</t>
+  </si>
+  <si>
+    <t>SIM7600E</t>
+  </si>
+  <si>
+    <t>Ár egyben:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;Ft&quot;;[Red]\-#,##0\ &quot;Ft&quot;"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,6 +88,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -94,9 +120,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hivatkozás" xfId="1" builtinId="8"/>
@@ -432,32 +465,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3876E43-79AD-4CB7-B6DE-977DB3E58EB9}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="66.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="C2" s="4">
+        <v>2340</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <f>SUM(C:C)</f>
+        <v>13483</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4">
+        <v>8575</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{3B843B76-4971-46CD-B8F3-C12257D6B3FA}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{7451AE47-9AB4-412E-910F-EC31B5FF6514}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{E219639D-FA77-4665-B41A-EB44944946B3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
